--- a/preprocess/examples/tracking/DEMO-E85-Em1/Live-Demo-Lumen3D-E85-Em1-30min-Positions-Analysis.xlsx
+++ b/preprocess/examples/tracking/DEMO-E85-Em1/Live-Demo-Lumen3D-E85-Em1-30min-Positions-Analysis.xlsx
@@ -467,7 +467,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>1000000001</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -492,7 +492,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1000000002</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -517,7 +517,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1000000003</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -542,7 +542,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>1000000004</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -567,7 +567,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>1000000005</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -592,7 +592,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>1000000006</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -617,7 +617,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>1000000007</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -642,7 +642,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>1000000008</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -667,7 +667,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1000000009</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -692,7 +692,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>1000000010</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -717,7 +717,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>1000000011</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -742,7 +742,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>1000000012</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -767,7 +767,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>1000000013</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>1000000014</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -817,7 +817,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>1000000015</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -842,7 +842,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>1000000016</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -867,7 +867,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>1000000017</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -892,7 +892,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>1000000018</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>1000000019</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -942,7 +942,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>1000000020</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>1000000021</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -992,7 +992,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>1000000022</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1017,7 +1017,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
+        <v>1000000023</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>24</v>
+        <v>1000000024</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -1067,7 +1067,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>25</v>
+        <v>1000000025</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -1092,7 +1092,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
+        <v>1000000026</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -1117,7 +1117,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>1000000027</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -1142,7 +1142,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>1000000028</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -1167,7 +1167,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>29</v>
+        <v>1000000029</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -1192,7 +1192,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>30</v>
+        <v>1000000030</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -1217,7 +1217,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>31</v>
+        <v>1000000031</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -1242,7 +1242,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>1000000032</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -1267,7 +1267,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>33</v>
+        <v>1000000033</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -1292,7 +1292,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>34</v>
+        <v>1000000034</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>35</v>
+        <v>1000000035</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -1342,7 +1342,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>36</v>
+        <v>1000000036</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -1367,7 +1367,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>37</v>
+        <v>1000000037</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -1392,7 +1392,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>38</v>
+        <v>1000000038</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -1417,7 +1417,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>39</v>
+        <v>1000000039</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -1442,7 +1442,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>40</v>
+        <v>1000000040</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -1467,7 +1467,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>41</v>
+        <v>1000000041</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -1492,7 +1492,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>42</v>
+        <v>1000000042</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -1517,7 +1517,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>43</v>
+        <v>1000000043</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -1542,7 +1542,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>44</v>
+        <v>1000000044</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -1567,7 +1567,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>45</v>
+        <v>1000000045</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -1592,7 +1592,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>46</v>
+        <v>1000000046</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -1617,7 +1617,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>47</v>
+        <v>1000000047</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -1642,7 +1642,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>48</v>
+        <v>1000000048</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -1667,7 +1667,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>1000000001</v>
       </c>
       <c r="C50" t="n">
         <v>2</v>
@@ -1692,7 +1692,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>1000000002</v>
       </c>
       <c r="C51" t="n">
         <v>2</v>
@@ -1717,7 +1717,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>1000000003</v>
       </c>
       <c r="C52" t="n">
         <v>2</v>
@@ -1742,7 +1742,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>1000000004</v>
       </c>
       <c r="C53" t="n">
         <v>2</v>
@@ -1767,7 +1767,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>5</v>
+        <v>1000000005</v>
       </c>
       <c r="C54" t="n">
         <v>2</v>
@@ -1792,7 +1792,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>6</v>
+        <v>1000000006</v>
       </c>
       <c r="C55" t="n">
         <v>2</v>
@@ -1817,7 +1817,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>7</v>
+        <v>1000000007</v>
       </c>
       <c r="C56" t="n">
         <v>2</v>
@@ -1842,7 +1842,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>8</v>
+        <v>1000000008</v>
       </c>
       <c r="C57" t="n">
         <v>2</v>
@@ -1867,7 +1867,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>9</v>
+        <v>1000000009</v>
       </c>
       <c r="C58" t="n">
         <v>2</v>
@@ -1892,7 +1892,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>10</v>
+        <v>1000000010</v>
       </c>
       <c r="C59" t="n">
         <v>2</v>
@@ -1917,7 +1917,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>11</v>
+        <v>1000000011</v>
       </c>
       <c r="C60" t="n">
         <v>2</v>
@@ -1942,7 +1942,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>12</v>
+        <v>1000000012</v>
       </c>
       <c r="C61" t="n">
         <v>2</v>
@@ -1967,7 +1967,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>13</v>
+        <v>1000000013</v>
       </c>
       <c r="C62" t="n">
         <v>2</v>
@@ -1992,7 +1992,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>14</v>
+        <v>1000000014</v>
       </c>
       <c r="C63" t="n">
         <v>2</v>
@@ -2017,7 +2017,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>15</v>
+        <v>1000000015</v>
       </c>
       <c r="C64" t="n">
         <v>2</v>
@@ -2042,7 +2042,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>16</v>
+        <v>1000000016</v>
       </c>
       <c r="C65" t="n">
         <v>2</v>
@@ -2067,7 +2067,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>17</v>
+        <v>1000000017</v>
       </c>
       <c r="C66" t="n">
         <v>2</v>
@@ -2092,7 +2092,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>18</v>
+        <v>1000000018</v>
       </c>
       <c r="C67" t="n">
         <v>2</v>
@@ -2117,7 +2117,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>19</v>
+        <v>1000000019</v>
       </c>
       <c r="C68" t="n">
         <v>2</v>
@@ -2142,7 +2142,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>20</v>
+        <v>1000000020</v>
       </c>
       <c r="C69" t="n">
         <v>2</v>
@@ -2167,7 +2167,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>21</v>
+        <v>1000000021</v>
       </c>
       <c r="C70" t="n">
         <v>2</v>
@@ -2192,7 +2192,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>22</v>
+        <v>1000000022</v>
       </c>
       <c r="C71" t="n">
         <v>2</v>
@@ -2217,7 +2217,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>23</v>
+        <v>1000000023</v>
       </c>
       <c r="C72" t="n">
         <v>2</v>
@@ -2242,7 +2242,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>24</v>
+        <v>1000000024</v>
       </c>
       <c r="C73" t="n">
         <v>2</v>
@@ -2267,7 +2267,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>25</v>
+        <v>1000000025</v>
       </c>
       <c r="C74" t="n">
         <v>2</v>
@@ -2292,7 +2292,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>26</v>
+        <v>1000000026</v>
       </c>
       <c r="C75" t="n">
         <v>2</v>
@@ -2317,7 +2317,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>27</v>
+        <v>1000000027</v>
       </c>
       <c r="C76" t="n">
         <v>2</v>
@@ -2342,7 +2342,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>28</v>
+        <v>1000000028</v>
       </c>
       <c r="C77" t="n">
         <v>2</v>
@@ -2367,7 +2367,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>29</v>
+        <v>1000000029</v>
       </c>
       <c r="C78" t="n">
         <v>2</v>
@@ -2392,7 +2392,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>30</v>
+        <v>1000000030</v>
       </c>
       <c r="C79" t="n">
         <v>2</v>
@@ -2417,7 +2417,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>31</v>
+        <v>1000000031</v>
       </c>
       <c r="C80" t="n">
         <v>2</v>
@@ -2442,7 +2442,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>32</v>
+        <v>1000000032</v>
       </c>
       <c r="C81" t="n">
         <v>2</v>
@@ -2467,7 +2467,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>33</v>
+        <v>1000000033</v>
       </c>
       <c r="C82" t="n">
         <v>2</v>
@@ -2492,7 +2492,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>34</v>
+        <v>1000000034</v>
       </c>
       <c r="C83" t="n">
         <v>2</v>
@@ -2517,7 +2517,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>35</v>
+        <v>1000000035</v>
       </c>
       <c r="C84" t="n">
         <v>2</v>
@@ -2542,7 +2542,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>36</v>
+        <v>1000000036</v>
       </c>
       <c r="C85" t="n">
         <v>2</v>
@@ -2567,7 +2567,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>37</v>
+        <v>1000000037</v>
       </c>
       <c r="C86" t="n">
         <v>2</v>
@@ -2592,7 +2592,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>38</v>
+        <v>1000000038</v>
       </c>
       <c r="C87" t="n">
         <v>2</v>
@@ -2617,7 +2617,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>39</v>
+        <v>1000000039</v>
       </c>
       <c r="C88" t="n">
         <v>2</v>
@@ -2642,7 +2642,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>40</v>
+        <v>1000000040</v>
       </c>
       <c r="C89" t="n">
         <v>2</v>
@@ -2667,7 +2667,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>41</v>
+        <v>1000000041</v>
       </c>
       <c r="C90" t="n">
         <v>2</v>
@@ -2692,7 +2692,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>42</v>
+        <v>1000000042</v>
       </c>
       <c r="C91" t="n">
         <v>2</v>
@@ -2717,7 +2717,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>43</v>
+        <v>1000000043</v>
       </c>
       <c r="C92" t="n">
         <v>2</v>
@@ -2742,7 +2742,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>44</v>
+        <v>1000000044</v>
       </c>
       <c r="C93" t="n">
         <v>2</v>
@@ -2767,7 +2767,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>45</v>
+        <v>1000000045</v>
       </c>
       <c r="C94" t="n">
         <v>2</v>
@@ -2792,7 +2792,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>46</v>
+        <v>1000000046</v>
       </c>
       <c r="C95" t="n">
         <v>2</v>
@@ -2817,7 +2817,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>47</v>
+        <v>1000000047</v>
       </c>
       <c r="C96" t="n">
         <v>2</v>
@@ -2842,7 +2842,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>48</v>
+        <v>1000000048</v>
       </c>
       <c r="C97" t="n">
         <v>2</v>
@@ -2867,7 +2867,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>1000000001</v>
       </c>
       <c r="C98" t="n">
         <v>3</v>
@@ -2892,7 +2892,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>2</v>
+        <v>1000000002</v>
       </c>
       <c r="C99" t="n">
         <v>3</v>
@@ -2917,7 +2917,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>3</v>
+        <v>1000000003</v>
       </c>
       <c r="C100" t="n">
         <v>3</v>
@@ -2942,7 +2942,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>4</v>
+        <v>1000000004</v>
       </c>
       <c r="C101" t="n">
         <v>3</v>
@@ -2967,7 +2967,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>5</v>
+        <v>1000000005</v>
       </c>
       <c r="C102" t="n">
         <v>3</v>
@@ -2992,7 +2992,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>6</v>
+        <v>1000000006</v>
       </c>
       <c r="C103" t="n">
         <v>3</v>
@@ -3017,7 +3017,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>7</v>
+        <v>1000000007</v>
       </c>
       <c r="C104" t="n">
         <v>3</v>
@@ -3042,7 +3042,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>8</v>
+        <v>1000000008</v>
       </c>
       <c r="C105" t="n">
         <v>3</v>
@@ -3067,7 +3067,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>9</v>
+        <v>1000000009</v>
       </c>
       <c r="C106" t="n">
         <v>3</v>
@@ -3092,7 +3092,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>10</v>
+        <v>1000000010</v>
       </c>
       <c r="C107" t="n">
         <v>3</v>
@@ -3117,7 +3117,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>11</v>
+        <v>1000000011</v>
       </c>
       <c r="C108" t="n">
         <v>3</v>
@@ -3142,7 +3142,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>12</v>
+        <v>1000000012</v>
       </c>
       <c r="C109" t="n">
         <v>3</v>
@@ -3167,7 +3167,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>13</v>
+        <v>1000000013</v>
       </c>
       <c r="C110" t="n">
         <v>3</v>
@@ -3192,7 +3192,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>14</v>
+        <v>1000000014</v>
       </c>
       <c r="C111" t="n">
         <v>3</v>
@@ -3217,7 +3217,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>15</v>
+        <v>1000000015</v>
       </c>
       <c r="C112" t="n">
         <v>3</v>
@@ -3242,7 +3242,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="n">
-        <v>16</v>
+        <v>1000000016</v>
       </c>
       <c r="C113" t="n">
         <v>3</v>
@@ -3267,7 +3267,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>17</v>
+        <v>1000000017</v>
       </c>
       <c r="C114" t="n">
         <v>3</v>
@@ -3292,7 +3292,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>18</v>
+        <v>1000000018</v>
       </c>
       <c r="C115" t="n">
         <v>3</v>
@@ -3317,7 +3317,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>19</v>
+        <v>1000000019</v>
       </c>
       <c r="C116" t="n">
         <v>3</v>
@@ -3342,7 +3342,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>20</v>
+        <v>1000000020</v>
       </c>
       <c r="C117" t="n">
         <v>3</v>
@@ -3367,7 +3367,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>21</v>
+        <v>1000000021</v>
       </c>
       <c r="C118" t="n">
         <v>3</v>
@@ -3392,7 +3392,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>22</v>
+        <v>1000000022</v>
       </c>
       <c r="C119" t="n">
         <v>3</v>
@@ -3417,7 +3417,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>49</v>
+        <v>1000000023</v>
       </c>
       <c r="C120" t="n">
         <v>3</v>
@@ -3442,7 +3442,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>50</v>
+        <v>1000000023</v>
       </c>
       <c r="C121" t="n">
         <v>3</v>
@@ -3467,7 +3467,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>24</v>
+        <v>1000000024</v>
       </c>
       <c r="C122" t="n">
         <v>3</v>
@@ -3492,7 +3492,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>25</v>
+        <v>1000000025</v>
       </c>
       <c r="C123" t="n">
         <v>3</v>
@@ -3517,7 +3517,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>26</v>
+        <v>1000000026</v>
       </c>
       <c r="C124" t="n">
         <v>3</v>
@@ -3542,7 +3542,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>27</v>
+        <v>1000000027</v>
       </c>
       <c r="C125" t="n">
         <v>3</v>
@@ -3567,7 +3567,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>28</v>
+        <v>1000000028</v>
       </c>
       <c r="C126" t="n">
         <v>3</v>
@@ -3592,7 +3592,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>29</v>
+        <v>1000000029</v>
       </c>
       <c r="C127" t="n">
         <v>3</v>
@@ -3617,7 +3617,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>30</v>
+        <v>1000000030</v>
       </c>
       <c r="C128" t="n">
         <v>3</v>
@@ -3642,7 +3642,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>31</v>
+        <v>1000000031</v>
       </c>
       <c r="C129" t="n">
         <v>3</v>
@@ -3667,7 +3667,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>32</v>
+        <v>1000000032</v>
       </c>
       <c r="C130" t="n">
         <v>3</v>
@@ -3692,7 +3692,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>33</v>
+        <v>1000000033</v>
       </c>
       <c r="C131" t="n">
         <v>3</v>
@@ -3717,7 +3717,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>34</v>
+        <v>1000000034</v>
       </c>
       <c r="C132" t="n">
         <v>3</v>
@@ -3742,7 +3742,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>35</v>
+        <v>1000000035</v>
       </c>
       <c r="C133" t="n">
         <v>3</v>
@@ -3767,7 +3767,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>36</v>
+        <v>1000000036</v>
       </c>
       <c r="C134" t="n">
         <v>3</v>
@@ -3792,7 +3792,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>37</v>
+        <v>1000000037</v>
       </c>
       <c r="C135" t="n">
         <v>3</v>
@@ -3817,7 +3817,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="n">
-        <v>38</v>
+        <v>1000000038</v>
       </c>
       <c r="C136" t="n">
         <v>3</v>
@@ -3842,7 +3842,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="n">
-        <v>39</v>
+        <v>1000000039</v>
       </c>
       <c r="C137" t="n">
         <v>3</v>
@@ -3867,7 +3867,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="n">
-        <v>40</v>
+        <v>1000000040</v>
       </c>
       <c r="C138" t="n">
         <v>3</v>
@@ -3892,7 +3892,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>41</v>
+        <v>1000000041</v>
       </c>
       <c r="C139" t="n">
         <v>3</v>
@@ -3917,7 +3917,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>42</v>
+        <v>1000000042</v>
       </c>
       <c r="C140" t="n">
         <v>3</v>
@@ -3942,7 +3942,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>43</v>
+        <v>1000000043</v>
       </c>
       <c r="C141" t="n">
         <v>3</v>
@@ -3967,7 +3967,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>44</v>
+        <v>1000000044</v>
       </c>
       <c r="C142" t="n">
         <v>3</v>
@@ -3992,7 +3992,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>45</v>
+        <v>1000000045</v>
       </c>
       <c r="C143" t="n">
         <v>3</v>
@@ -4017,7 +4017,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>46</v>
+        <v>1000000046</v>
       </c>
       <c r="C144" t="n">
         <v>3</v>
@@ -4042,7 +4042,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="n">
-        <v>47</v>
+        <v>1000000047</v>
       </c>
       <c r="C145" t="n">
         <v>3</v>
@@ -4067,7 +4067,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>48</v>
+        <v>1000000048</v>
       </c>
       <c r="C146" t="n">
         <v>3</v>
@@ -4092,7 +4092,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>1</v>
+        <v>1000000001</v>
       </c>
       <c r="C147" t="n">
         <v>4</v>
@@ -4117,7 +4117,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>2</v>
+        <v>1000000002</v>
       </c>
       <c r="C148" t="n">
         <v>4</v>
@@ -4142,7 +4142,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>3</v>
+        <v>1000000003</v>
       </c>
       <c r="C149" t="n">
         <v>4</v>
@@ -4167,7 +4167,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>4</v>
+        <v>1000000004</v>
       </c>
       <c r="C150" t="n">
         <v>4</v>
@@ -4192,7 +4192,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>5</v>
+        <v>1000000005</v>
       </c>
       <c r="C151" t="n">
         <v>4</v>
@@ -4217,7 +4217,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>6</v>
+        <v>1000000006</v>
       </c>
       <c r="C152" t="n">
         <v>4</v>
@@ -4242,7 +4242,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>7</v>
+        <v>1000000007</v>
       </c>
       <c r="C153" t="n">
         <v>4</v>
@@ -4267,7 +4267,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>8</v>
+        <v>1000000008</v>
       </c>
       <c r="C154" t="n">
         <v>4</v>
@@ -4292,7 +4292,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>9</v>
+        <v>1000000009</v>
       </c>
       <c r="C155" t="n">
         <v>4</v>
@@ -4317,7 +4317,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>10</v>
+        <v>1000000010</v>
       </c>
       <c r="C156" t="n">
         <v>4</v>
@@ -4342,7 +4342,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>11</v>
+        <v>1000000011</v>
       </c>
       <c r="C157" t="n">
         <v>4</v>
@@ -4367,7 +4367,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>12</v>
+        <v>1000000012</v>
       </c>
       <c r="C158" t="n">
         <v>4</v>
@@ -4392,7 +4392,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>13</v>
+        <v>1000000013</v>
       </c>
       <c r="C159" t="n">
         <v>4</v>
@@ -4417,7 +4417,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>14</v>
+        <v>1000000014</v>
       </c>
       <c r="C160" t="n">
         <v>4</v>
@@ -4442,7 +4442,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>15</v>
+        <v>1000000015</v>
       </c>
       <c r="C161" t="n">
         <v>4</v>
@@ -4467,7 +4467,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>16</v>
+        <v>1000000016</v>
       </c>
       <c r="C162" t="n">
         <v>4</v>
@@ -4492,7 +4492,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>17</v>
+        <v>1000000017</v>
       </c>
       <c r="C163" t="n">
         <v>4</v>
@@ -4517,7 +4517,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>18</v>
+        <v>1000000018</v>
       </c>
       <c r="C164" t="n">
         <v>4</v>
@@ -4542,7 +4542,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>19</v>
+        <v>1000000019</v>
       </c>
       <c r="C165" t="n">
         <v>4</v>
@@ -4567,7 +4567,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>20</v>
+        <v>1000000020</v>
       </c>
       <c r="C166" t="n">
         <v>4</v>
@@ -4592,7 +4592,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>21</v>
+        <v>1000000021</v>
       </c>
       <c r="C167" t="n">
         <v>4</v>
@@ -4617,7 +4617,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>22</v>
+        <v>1000000022</v>
       </c>
       <c r="C168" t="n">
         <v>4</v>
@@ -4642,7 +4642,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>49</v>
+        <v>1000000023</v>
       </c>
       <c r="C169" t="n">
         <v>4</v>
@@ -4667,7 +4667,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>50</v>
+        <v>1000000023</v>
       </c>
       <c r="C170" t="n">
         <v>4</v>
@@ -4692,7 +4692,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>24</v>
+        <v>1000000024</v>
       </c>
       <c r="C171" t="n">
         <v>4</v>
@@ -4717,7 +4717,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="n">
-        <v>25</v>
+        <v>1000000025</v>
       </c>
       <c r="C172" t="n">
         <v>4</v>
@@ -4742,7 +4742,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="n">
-        <v>26</v>
+        <v>1000000026</v>
       </c>
       <c r="C173" t="n">
         <v>4</v>
@@ -4767,7 +4767,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>27</v>
+        <v>1000000027</v>
       </c>
       <c r="C174" t="n">
         <v>4</v>
@@ -4792,7 +4792,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>28</v>
+        <v>1000000028</v>
       </c>
       <c r="C175" t="n">
         <v>4</v>
@@ -4817,7 +4817,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>29</v>
+        <v>1000000029</v>
       </c>
       <c r="C176" t="n">
         <v>4</v>
@@ -4842,7 +4842,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="n">
-        <v>30</v>
+        <v>1000000030</v>
       </c>
       <c r="C177" t="n">
         <v>4</v>
@@ -4867,7 +4867,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="n">
-        <v>31</v>
+        <v>1000000031</v>
       </c>
       <c r="C178" t="n">
         <v>4</v>
@@ -4892,7 +4892,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="n">
-        <v>32</v>
+        <v>1000000032</v>
       </c>
       <c r="C179" t="n">
         <v>4</v>
@@ -4917,7 +4917,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>33</v>
+        <v>1000000033</v>
       </c>
       <c r="C180" t="n">
         <v>4</v>
@@ -4942,7 +4942,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>34</v>
+        <v>1000000034</v>
       </c>
       <c r="C181" t="n">
         <v>4</v>
@@ -4967,7 +4967,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>35</v>
+        <v>1000000035</v>
       </c>
       <c r="C182" t="n">
         <v>4</v>
@@ -4992,7 +4992,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="n">
-        <v>36</v>
+        <v>1000000036</v>
       </c>
       <c r="C183" t="n">
         <v>4</v>
@@ -5017,7 +5017,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="n">
-        <v>37</v>
+        <v>1000000037</v>
       </c>
       <c r="C184" t="n">
         <v>4</v>
@@ -5042,7 +5042,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>38</v>
+        <v>1000000038</v>
       </c>
       <c r="C185" t="n">
         <v>4</v>
@@ -5067,7 +5067,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="n">
-        <v>39</v>
+        <v>1000000039</v>
       </c>
       <c r="C186" t="n">
         <v>4</v>
@@ -5092,7 +5092,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="n">
-        <v>40</v>
+        <v>1000000040</v>
       </c>
       <c r="C187" t="n">
         <v>4</v>
@@ -5117,7 +5117,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="n">
-        <v>41</v>
+        <v>1000000041</v>
       </c>
       <c r="C188" t="n">
         <v>4</v>
@@ -5142,7 +5142,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="n">
-        <v>42</v>
+        <v>1000000042</v>
       </c>
       <c r="C189" t="n">
         <v>4</v>
@@ -5167,7 +5167,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="n">
-        <v>43</v>
+        <v>1000000043</v>
       </c>
       <c r="C190" t="n">
         <v>4</v>
@@ -5192,7 +5192,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="n">
-        <v>44</v>
+        <v>1000000044</v>
       </c>
       <c r="C191" t="n">
         <v>4</v>
@@ -5217,7 +5217,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="n">
-        <v>45</v>
+        <v>1000000045</v>
       </c>
       <c r="C192" t="n">
         <v>4</v>
@@ -5242,7 +5242,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="n">
-        <v>46</v>
+        <v>1000000046</v>
       </c>
       <c r="C193" t="n">
         <v>4</v>
@@ -5267,7 +5267,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>47</v>
+        <v>1000000047</v>
       </c>
       <c r="C194" t="n">
         <v>4</v>
@@ -5292,7 +5292,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>48</v>
+        <v>1000000048</v>
       </c>
       <c r="C195" t="n">
         <v>4</v>
